--- a/main/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="195">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -452,6 +452,9 @@
   </si>
   <si>
     <t>Voie d'administration</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>EDQM (0.4.0.127.0.16.1.1.2.1)</t>
@@ -2929,10 +2932,10 @@
         <v>73</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>73</v>
@@ -2970,10 +2973,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2996,13 +2999,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3053,7 +3056,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3070,10 +3073,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3096,13 +3099,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3153,7 +3156,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3170,10 +3173,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3199,10 +3202,10 @@
         <v>80</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3253,7 +3256,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3270,10 +3273,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3299,10 +3302,10 @@
         <v>80</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3353,7 +3356,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3370,10 +3373,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3399,10 +3402,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3429,10 +3432,10 @@
         <v>73</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>73</v>
@@ -3453,7 +3456,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3465,15 +3468,15 @@
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3496,13 +3499,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3553,7 +3556,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3570,14 +3573,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -3596,16 +3599,16 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3643,19 +3646,19 @@
         <v>73</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3667,15 +3670,15 @@
         <v>73</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3695,22 +3698,22 @@
         <v>73</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>73</v>
@@ -3759,7 +3762,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3771,15 +3774,15 @@
         <v>73</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3799,22 +3802,22 @@
         <v>73</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>73</v>
@@ -3863,7 +3866,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3875,15 +3878,15 @@
         <v>73</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3909,10 +3912,10 @@
         <v>131</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3939,10 +3942,10 @@
         <v>73</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>73</v>
@@ -3963,7 +3966,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3980,10 +3983,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4006,13 +4009,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4063,7 +4066,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4080,10 +4083,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4106,13 +4109,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4163,7 +4166,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
